--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/aae/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>395</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>426</v>
